--- a/statistic/stat.xlsx
+++ b/statistic/stat.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Алгоритм</t>
   </si>
@@ -33,19 +33,10 @@
     <t>ShortestBFS</t>
   </si>
   <si>
-    <t xml:space="preserve">люблю, люблю, Моё, аниме, Моё, аниме, Моё, аниме,</t>
-  </si>
-  <si>
     <t>ProbbestDijkstra</t>
   </si>
   <si>
-    <t xml:space="preserve">тестирую, скажешь, теста, Давай, последний, </t>
-  </si>
-  <si>
     <t>KbestBFS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">завоз, </t>
   </si>
   <si>
     <t>KlenBFS</t>
@@ -101,8 +92,12 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -603,7 +598,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="1" max="1" width="15.7109375"/>
-    <col bestFit="1" min="2" max="2" width="8.8515625"/>
+    <col bestFit="1" min="2" max="2" style="1" width="8.8515625"/>
     <col bestFit="1" min="3" max="3" width="11.00390625"/>
     <col bestFit="1" min="4" max="4" width="13.7109375"/>
   </cols>
@@ -612,7 +607,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -626,159 +621,240 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <f>D2/C2</f>
-        <v>0</v>
+        <v>3.4444444444444446</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>5</v>
+        <v>31</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="H2">
+        <f>C2+F2</f>
+        <v>9</v>
+      </c>
+      <c r="I2">
+        <f>D2+G2</f>
+        <v>31</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1">
         <f>D3/C3</f>
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="H3">
+        <f>C3+F3</f>
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <f>D3+G3</f>
+        <v>2</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1">
         <f>D4/C4</f>
-        <v>2.6000000000000001</v>
+        <v>1.8333333333333333</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D4">
-        <v>13</v>
-      </c>
-      <c r="H4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="H4">
+        <f>C4+F4</f>
+        <v>18</v>
+      </c>
+      <c r="I4">
+        <f>D4+G4</f>
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1">
         <f>D5/C5</f>
-        <v>0</v>
+        <v>1.2222222222222223</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="H5">
+        <f>C5+F5</f>
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <f>D5+G5</f>
+        <v>11</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
         <f>D6/C6</f>
-        <v>1</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
+      <c r="F6" s="2"/>
+      <c r="H6">
+        <f>C6+F6</f>
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <f>D6+G6</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="e">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1">
         <f>D7/C7</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
+      <c r="F7" s="2"/>
+      <c r="H7">
+        <f>C7+F7</f>
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <f>D7+G7</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1">
         <f>D8/C8</f>
-        <v>6</v>
+        <v>2.375</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="H8">
+        <f>C8+F8</f>
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <f>D8+G8</f>
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1">
         <f>D9/C9</f>
+        <v>1.2</v>
+      </c>
+      <c r="C9">
         <v>10</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
       <c r="D9">
+        <v>12</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="H9">
+        <f>C9+F9</f>
         <v>10</v>
+      </c>
+      <c r="I9">
+        <f>D9+G9</f>
+        <v>12</v>
       </c>
     </row>
     <row r="10" ht="14.25">
       <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1">
         <f>D10/C10</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="H10">
+        <f>C10+F10</f>
+        <v>7</v>
+      </c>
+      <c r="I10">
+        <f>D10+G10</f>
+        <v>7</v>
       </c>
     </row>
     <row r="11" ht="14.25">
       <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="e">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1">
         <f>D11/C11</f>
-        <v>#DIV/0!</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="H11">
+        <f>C11+F11</f>
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <f>D11+G11</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/statistic/stat.xlsx
+++ b/statistic/stat.xlsx
@@ -622,22 +622,22 @@
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <f>D2/C2</f>
-        <v>3.4444444444444446</v>
+        <f t="shared" ref="B2:B9" si="0">D2/C2</f>
+        <v>3.1000000000000001</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>31</v>
       </c>
       <c r="F2" s="2"/>
       <c r="H2">
-        <f>C2+F2</f>
-        <v>9</v>
+        <f t="shared" ref="H2:H9" si="1">C2+F2</f>
+        <v>10</v>
       </c>
       <c r="I2">
-        <f>D2+G2</f>
+        <f t="shared" ref="I2:I9" si="2">D2+G2</f>
         <v>31</v>
       </c>
     </row>
@@ -646,23 +646,23 @@
         <v>5</v>
       </c>
       <c r="B3" s="1">
-        <f>D3/C3</f>
-        <v>0.25</v>
+        <f t="shared" si="0"/>
+        <v>0.30769230769230771</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2"/>
       <c r="H3">
-        <f>C3+F3</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="I3">
-        <f>D3+G3</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
     </row>
     <row r="4" ht="14.25">
@@ -670,7 +670,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1">
-        <f>D4/C4</f>
+        <f t="shared" si="0"/>
         <v>1.8333333333333333</v>
       </c>
       <c r="C4">
@@ -681,11 +681,11 @@
       </c>
       <c r="F4" s="2"/>
       <c r="H4">
-        <f>C4+F4</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="I4">
-        <f>D4+G4</f>
+        <f t="shared" si="2"/>
         <v>33</v>
       </c>
     </row>
@@ -694,22 +694,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="1">
-        <f>D5/C5</f>
-        <v>1.2222222222222223</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <v>11</v>
       </c>
       <c r="F5" s="2"/>
       <c r="H5">
-        <f>C5+F5</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="I5">
-        <f>D5+G5</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
     </row>
@@ -718,22 +718,22 @@
         <v>8</v>
       </c>
       <c r="B6" s="1">
-        <f>D6/C6</f>
-        <v>0.20000000000000001</v>
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="F6" s="2"/>
       <c r="H6">
-        <f>C6+F6</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="I6">
-        <f>D6+G6</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -742,22 +742,22 @@
         <v>9</v>
       </c>
       <c r="B7" s="1">
-        <f>D7/C7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="F7" s="2"/>
       <c r="H7">
-        <f>C7+F7</f>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="I7">
-        <f>D7+G7</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -766,22 +766,22 @@
         <v>10</v>
       </c>
       <c r="B8" s="1">
-        <f>D8/C8</f>
-        <v>2.375</v>
+        <f t="shared" si="0"/>
+        <v>1.7272727272727273</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D8">
         <v>19</v>
       </c>
       <c r="F8" s="2"/>
       <c r="H8">
-        <f>C8+F8</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="I8">
-        <f>D8+G8</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
     </row>
@@ -790,7 +790,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="1">
-        <f>D9/C9</f>
+        <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
       <c r="C9">
@@ -801,11 +801,11 @@
       </c>
       <c r="F9" s="2"/>
       <c r="H9">
-        <f>C9+F9</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I9">
-        <f>D9+G9</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
     </row>
@@ -814,22 +814,22 @@
         <v>12</v>
       </c>
       <c r="B10" s="1">
-        <f>D10/C10</f>
-        <v>1</v>
+        <f t="shared" ref="B10:B11" si="3">D10/C10</f>
+        <v>0.875</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>7</v>
       </c>
       <c r="F10" s="2"/>
       <c r="H10">
-        <f>C10+F10</f>
-        <v>7</v>
+        <f t="shared" ref="H10:H11" si="4">C10+F10</f>
+        <v>8</v>
       </c>
       <c r="I10">
-        <f>D10+G10</f>
+        <f t="shared" ref="I10:I11" si="5">D10+G10</f>
         <v>7</v>
       </c>
     </row>
@@ -838,23 +838,23 @@
         <v>13</v>
       </c>
       <c r="B11" s="1">
-        <f>D11/C11</f>
-        <v>0.20000000000000001</v>
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2"/>
       <c r="H11">
-        <f>C11+F11</f>
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>6</v>
       </c>
       <c r="I11">
-        <f>D11+G11</f>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/statistic/stat.xlsx
+++ b/statistic/stat.xlsx
@@ -623,22 +623,22 @@
       </c>
       <c r="B2" s="1">
         <f t="shared" ref="B2:B9" si="0">D2/C2</f>
-        <v>3.1000000000000001</v>
+        <v>2.8181818181818183</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="F2" s="2"/>
       <c r="H2">
         <f t="shared" ref="H2:H9" si="1">C2+F2</f>
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I9" si="2">D2+G2</f>
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" ht="14.25">
@@ -647,22 +647,22 @@
       </c>
       <c r="B3" s="1">
         <f t="shared" si="0"/>
-        <v>0.30769230769230771</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2"/>
       <c r="H3">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" ht="14.25">
@@ -671,22 +671,22 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F4" s="2"/>
       <c r="H4">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I4">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" ht="14.25">
@@ -695,22 +695,22 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.1818181818181819</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F5" s="2"/>
       <c r="H5">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I5">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="14.25">
@@ -719,10 +719,10 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
+        <v>0.11764705882352941</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -730,7 +730,7 @@
       <c r="F6" s="2"/>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I6">
         <f t="shared" si="2"/>
@@ -743,22 +743,22 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.14999999999999999</v>
       </c>
       <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
         <v>3</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
       </c>
       <c r="F7" s="2"/>
       <c r="H7">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="14.25">
@@ -767,22 +767,22 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>1.7272727272727273</v>
+        <v>1.0952380952380953</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F8" s="2"/>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I8">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="14.25">
@@ -791,22 +791,22 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.2608695652173914</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F9" s="2"/>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="14.25">
@@ -815,22 +815,22 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" ref="B10:B11" si="3">D10/C10</f>
-        <v>0.875</v>
+        <v>2.5</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="F10" s="2"/>
       <c r="H10">
         <f t="shared" ref="H10:H11" si="4">C10+F10</f>
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I10">
         <f t="shared" ref="I10:I11" si="5">D10+G10</f>
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="14.25">
@@ -839,22 +839,22 @@
       </c>
       <c r="B11" s="1">
         <f t="shared" si="3"/>
-        <v>0.33333333333333331</v>
+        <v>0.59090909090909094</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F11" s="2"/>
       <c r="H11">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="I11">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/statistic/stat.xlsx
+++ b/statistic/stat.xlsx
@@ -623,22 +623,22 @@
       </c>
       <c r="B2" s="1">
         <f t="shared" ref="B2:B9" si="0">D2/C2</f>
-        <v>2.8181818181818183</v>
+        <v>2.7894736842105261</v>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D2">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F2" s="2"/>
       <c r="H2">
         <f t="shared" ref="H2:H9" si="1">C2+F2</f>
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I9" si="2">D2+G2</f>
-        <v>62</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" ht="14.25">
@@ -647,22 +647,22 @@
       </c>
       <c r="B3" s="1">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
+        <v>1.0689655172413792</v>
       </c>
       <c r="C3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F3" s="2"/>
       <c r="H3">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" ht="14.25">
@@ -674,19 +674,19 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F4" s="2"/>
       <c r="H4">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I4">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" ht="14.25">
@@ -695,22 +695,22 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>1.1818181818181819</v>
+        <v>1.6923076923076923</v>
       </c>
       <c r="C5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2"/>
       <c r="H5">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I5">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" ht="14.25">
@@ -719,22 +719,22 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>0.11764705882352941</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="C6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2"/>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="14.25">
@@ -743,22 +743,22 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>0.14999999999999999</v>
+        <v>0.30434782608695654</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2"/>
       <c r="H7">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" ht="14.25">
@@ -767,22 +767,22 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>1.0952380952380953</v>
+        <v>1.125</v>
       </c>
       <c r="C8">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F8" s="2"/>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I8">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="14.25">
@@ -791,22 +791,22 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>1.2608695652173914</v>
+        <v>1.28</v>
       </c>
       <c r="C9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F9" s="2"/>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" ht="14.25">
@@ -815,22 +815,22 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" ref="B10:B11" si="3">D10/C10</f>
-        <v>2.5</v>
+        <v>2.4782608695652173</v>
       </c>
       <c r="C10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F10" s="2"/>
       <c r="H10">
         <f t="shared" ref="H10:H11" si="4">C10+F10</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I10">
         <f t="shared" ref="I10:I11" si="5">D10+G10</f>
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="14.25">
@@ -839,22 +839,22 @@
       </c>
       <c r="B11" s="1">
         <f t="shared" si="3"/>
-        <v>0.59090909090909094</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="C11">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F11" s="2"/>
       <c r="H11">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I11">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/statistic/stat.xlsx
+++ b/statistic/stat.xlsx
@@ -92,9 +92,10 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -113,6 +114,962 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" spc="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr/>
+              <a:t>Точность ответов</a:t>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout/>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Лист1'!$A$2:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Лист1'!$B$2:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.19747899159663868</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10857142857142857</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1975</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.20833333333333334</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.04285714285714286</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.029629629629629627</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.203125</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.225</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.04871794871794872</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-26"/>
+        <c:axId val="1001"/>
+        <c:axId val="1002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm>
+      <a:off x="5600699" y="2433637"/>
+      <a:ext cx="5124449" cy="3186112"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>485774</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>123824</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="833652870" name=""/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="5600699" y="2433637"/>
+        <a:ext cx="5124449" cy="3186112"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
@@ -621,240 +1578,240 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1">
-        <f t="shared" ref="B2:B9" si="0">D2/C2</f>
-        <v>2.7894736842105261</v>
+      <c r="B2" s="2">
+        <f>D2/C2/10</f>
+        <v>0.19747899159663868</v>
       </c>
       <c r="C2">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="D2">
-        <v>106</v>
-      </c>
-      <c r="F2" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="F2" s="3"/>
       <c r="H2">
-        <f t="shared" ref="H2:H9" si="1">C2+F2</f>
-        <v>38</v>
+        <f t="shared" ref="H2:H9" si="0">C2+F2</f>
+        <v>119</v>
       </c>
       <c r="I2">
-        <f t="shared" ref="I2:I9" si="2">D2+G2</f>
-        <v>106</v>
+        <f t="shared" ref="I2:I9" si="1">D2+G2</f>
+        <v>235</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
+        <f>D3/C3/10</f>
+        <v>0.10857142857142857</v>
+      </c>
+      <c r="C3">
+        <v>35</v>
+      </c>
+      <c r="D3">
+        <v>38</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="H3">
         <f t="shared" si="0"/>
-        <v>1.0689655172413792</v>
-      </c>
-      <c r="C3">
-        <v>29</v>
-      </c>
-      <c r="D3">
-        <v>31</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="H3">
+        <v>35</v>
+      </c>
+      <c r="I3">
         <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="I3">
-        <f t="shared" si="2"/>
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
+        <f>D4/C4/10</f>
+        <v>0.19750000000000001</v>
+      </c>
+      <c r="C4">
+        <v>40</v>
+      </c>
+      <c r="D4">
+        <v>79</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="H4">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>33</v>
-      </c>
-      <c r="D4">
-        <v>66</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="H4">
+        <v>40</v>
+      </c>
+      <c r="I4">
         <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="2"/>
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
+        <f>D5/C5/10</f>
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="C5">
+        <v>36</v>
+      </c>
+      <c r="D5">
+        <v>75</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="H5">
         <f t="shared" si="0"/>
-        <v>1.6923076923076923</v>
-      </c>
-      <c r="C5">
-        <v>26</v>
-      </c>
-      <c r="D5">
-        <v>44</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="H5">
+        <v>36</v>
+      </c>
+      <c r="I5">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="2"/>
-        <v>44</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
+        <f>D6/C6/10</f>
+        <v>0.042857142857142858</v>
+      </c>
+      <c r="C6">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="H6">
         <f t="shared" si="0"/>
-        <v>0.27777777777777779</v>
-      </c>
-      <c r="C6">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="H6">
+        <v>21</v>
+      </c>
+      <c r="I6">
         <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
+        <f>D7/C7/10</f>
+        <v>0.029629629629629627</v>
+      </c>
+      <c r="C7">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="H7">
         <f t="shared" si="0"/>
-        <v>0.30434782608695654</v>
-      </c>
-      <c r="C7">
-        <v>23</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="H7">
+        <v>27</v>
+      </c>
+      <c r="I7">
         <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2">
+        <f>D8/C8/10</f>
+        <v>0.125</v>
+      </c>
+      <c r="C8">
+        <v>32</v>
+      </c>
+      <c r="D8">
+        <v>40</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="H8">
         <f t="shared" si="0"/>
-        <v>1.125</v>
-      </c>
-      <c r="C8">
-        <v>24</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="H8">
+        <v>32</v>
+      </c>
+      <c r="I8">
         <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="2"/>
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="2">
+        <f>D9/C9/10</f>
+        <v>0.203125</v>
+      </c>
+      <c r="C9">
+        <v>32</v>
+      </c>
+      <c r="D9">
+        <v>65</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="H9">
         <f t="shared" si="0"/>
-        <v>1.28</v>
-      </c>
-      <c r="C9">
-        <v>25</v>
-      </c>
-      <c r="D9">
         <v>32</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="H9">
+      <c r="I9">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="2"/>
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" ht="14.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="1">
-        <f t="shared" ref="B10:B11" si="3">D10/C10</f>
-        <v>2.4782608695652173</v>
+      <c r="B10" s="2">
+        <f>D10/C10/10</f>
+        <v>0.22500000000000001</v>
       </c>
       <c r="C10">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D10">
-        <v>57</v>
-      </c>
-      <c r="F10" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="F10" s="3"/>
       <c r="H10">
-        <f t="shared" ref="H10:H11" si="4">C10+F10</f>
-        <v>23</v>
+        <f t="shared" ref="H10:H11" si="2">C10+F10</f>
+        <v>32</v>
       </c>
       <c r="I10">
-        <f t="shared" ref="I10:I11" si="5">D10+G10</f>
-        <v>57</v>
+        <f t="shared" ref="I10:I11" si="3">D10+G10</f>
+        <v>72</v>
       </c>
     </row>
     <row r="11" ht="14.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="2">
+        <f>D11/C11/10</f>
+        <v>0.048717948717948718</v>
+      </c>
+      <c r="C11">
+        <v>39</v>
+      </c>
+      <c r="D11">
+        <v>19</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="H11">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="I11">
         <f t="shared" si="3"/>
-        <v>0.6071428571428571</v>
-      </c>
-      <c r="C11">
-        <v>28</v>
-      </c>
-      <c r="D11">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="H11">
-        <f t="shared" si="4"/>
-        <v>28</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="5"/>
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -862,5 +1819,6 @@
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/statistic/stat.xlsx
+++ b/statistic/stat.xlsx
@@ -223,39 +223,47 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.19747899159663868</c:v>
+                  <c:v>0.17969924812030075</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.10857142857142857</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1975</c:v>
+                  <c:v>0.21707317073170734</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.20833333333333334</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.04285714285714286</c:v>
+                  <c:v>0.0391304347826087</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.029629629629629627</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.125</c:v>
+                  <c:v>0.12121212121212122</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.203125</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.225</c:v>
+                  <c:v>0.19206349206349208</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.04871794871794872</c:v>
+                  <c:v>0.056097560975609764</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:dLbls>
+          <c:showBubbleSize val="0"/>
+          <c:showCatName val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showPercent val="0"/>
+          <c:showSerName val="0"/>
+          <c:showVal val="0"/>
+        </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-26"/>
         <c:axId val="1001"/>
@@ -422,7 +430,7 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr bwMode="auto">
-    <a:xfrm>
+    <a:xfrm rot="0">
       <a:off x="5600699" y="2433637"/>
       <a:ext cx="5124449" cy="3186112"/>
     </a:xfrm>
@@ -1057,7 +1065,7 @@
           <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
+      <xdr:xfrm rot="0">
         <a:off x="5600699" y="2433637"/>
         <a:ext cx="5124449" cy="3186112"/>
       </xdr:xfrm>
@@ -1579,23 +1587,23 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <f>D2/C2/10</f>
-        <v>0.19747899159663868</v>
+        <f t="shared" ref="B2:B9" si="0">D2/C2/10</f>
+        <v>0.1902097902097902</v>
       </c>
       <c r="C2">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="D2">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="F2" s="3"/>
       <c r="H2">
-        <f t="shared" ref="H2:H9" si="0">C2+F2</f>
-        <v>119</v>
+        <f t="shared" ref="H2:H9" si="1">C2+F2</f>
+        <v>143</v>
       </c>
       <c r="I2">
-        <f t="shared" ref="I2:I9" si="1">D2+G2</f>
-        <v>235</v>
+        <f t="shared" ref="I2:I9" si="2">D2+G2</f>
+        <v>272</v>
       </c>
     </row>
     <row r="3" ht="14.25">
@@ -1603,23 +1611,23 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <f>D3/C3/10</f>
-        <v>0.10857142857142857</v>
+        <f t="shared" si="0"/>
+        <v>0.10263157894736843</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F3" s="3"/>
       <c r="H3">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="I3">
         <f t="shared" si="1"/>
         <v>38</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="2"/>
+        <v>39</v>
       </c>
     </row>
     <row r="4" ht="14.25">
@@ -1627,23 +1635,23 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <f>D4/C4/10</f>
-        <v>0.19750000000000001</v>
+        <f t="shared" si="0"/>
+        <v>0.23404255319148937</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D4">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="F4" s="3"/>
       <c r="H4">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>47</v>
       </c>
       <c r="I4">
-        <f t="shared" si="1"/>
-        <v>79</v>
+        <f t="shared" si="2"/>
+        <v>110</v>
       </c>
     </row>
     <row r="5" ht="14.25">
@@ -1651,22 +1659,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <f>D5/C5/10</f>
-        <v>0.20833333333333334</v>
+        <f t="shared" si="0"/>
+        <v>0.20270270270270271</v>
       </c>
       <c r="C5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5">
         <v>75</v>
       </c>
       <c r="F5" s="3"/>
       <c r="H5">
-        <f t="shared" si="0"/>
-        <v>36</v>
+        <f t="shared" si="1"/>
+        <v>37</v>
       </c>
       <c r="I5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>75</v>
       </c>
     </row>
@@ -1675,23 +1683,23 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <f>D6/C6/10</f>
-        <v>0.042857142857142858</v>
+        <f t="shared" si="0"/>
+        <v>0.082758620689655171</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F6" s="3"/>
       <c r="H6">
-        <f t="shared" si="0"/>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>29</v>
       </c>
       <c r="I6">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="14.25">
@@ -1699,23 +1707,23 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <f>D7/C7/10</f>
-        <v>0.029629629629629627</v>
+        <f t="shared" si="0"/>
+        <v>0.069696969696969702</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F7" s="3"/>
       <c r="H7">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <f t="shared" si="1"/>
+        <v>33</v>
       </c>
       <c r="I7">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f t="shared" si="2"/>
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="14.25">
@@ -1723,23 +1731,23 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <f>D8/C8/10</f>
-        <v>0.125</v>
+        <f t="shared" si="0"/>
+        <v>0.14473684210526316</v>
       </c>
       <c r="C8">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D8">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F8" s="3"/>
       <c r="H8">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>38</v>
       </c>
       <c r="I8">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <f t="shared" si="2"/>
+        <v>55</v>
       </c>
     </row>
     <row r="9" ht="14.25">
@@ -1747,23 +1755,23 @@
         <v>11</v>
       </c>
       <c r="B9" s="2">
-        <f>D9/C9/10</f>
-        <v>0.203125</v>
+        <f t="shared" si="0"/>
+        <v>0.21428571428571427</v>
       </c>
       <c r="C9">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D9">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F9" s="3"/>
       <c r="H9">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>35</v>
       </c>
       <c r="I9">
-        <f t="shared" si="1"/>
-        <v>65</v>
+        <f t="shared" si="2"/>
+        <v>75</v>
       </c>
     </row>
     <row r="10" ht="14.25">
@@ -1771,23 +1779,23 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <f>D10/C10/10</f>
-        <v>0.22500000000000001</v>
+        <f t="shared" ref="B10:B11" si="3">D10/C10/10</f>
+        <v>0.19848484848484849</v>
       </c>
       <c r="C10">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="D10">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="F10" s="3"/>
       <c r="H10">
-        <f t="shared" ref="H10:H11" si="2">C10+F10</f>
-        <v>32</v>
+        <f t="shared" ref="H10:H11" si="4">C10+F10</f>
+        <v>66</v>
       </c>
       <c r="I10">
-        <f t="shared" ref="I10:I11" si="3">D10+G10</f>
-        <v>72</v>
+        <f t="shared" ref="I10:I11" si="5">D10+G10</f>
+        <v>131</v>
       </c>
     </row>
     <row r="11" ht="14.25">
@@ -1795,23 +1803,23 @@
         <v>13</v>
       </c>
       <c r="B11" s="2">
-        <f>D11/C11/10</f>
-        <v>0.048717948717948718</v>
+        <f t="shared" si="3"/>
+        <v>0.052272727272727269</v>
       </c>
       <c r="C11">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D11">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F11" s="3"/>
       <c r="H11">
-        <f t="shared" si="2"/>
-        <v>39</v>
+        <f t="shared" si="4"/>
+        <v>44</v>
       </c>
       <c r="I11">
-        <f t="shared" si="3"/>
-        <v>19</v>
+        <f t="shared" si="5"/>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
